--- a/sheet.xlsx
+++ b/sheet.xlsx
@@ -246,7 +246,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -255,58 +255,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -487,74 +435,146 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -847,655 +867,657 @@
     <col min="10" max="10" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="6:10" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="I4" s="6" t="s">
+    <row r="4" spans="2:10" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="I4" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="6:10" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F6" s="1" t="s">
+    <row r="5" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:10" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F6" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="25" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="6:10" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="4" t="s">
+    <row r="7" spans="2:10" ht="38.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="19"/>
+      <c r="F7" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="28">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="6:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" s="4" t="s">
+    <row r="8" spans="2:10" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F8" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="33">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G9" s="4" t="s">
+    <row r="9" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F9" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="31">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="4" t="s">
+    <row r="10" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F10" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="G10" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="34">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="4" t="s">
+    <row r="11" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F11" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="31">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="4" t="s">
+    <row r="12" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F12" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="34">
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="4" t="s">
+    <row r="13" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F13" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="J13" s="31">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="34">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G15" s="4" t="s">
+    <row r="15" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F15" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="G15" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="23">
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="6:10" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F16" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="4" t="s">
+    <row r="16" spans="2:10" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F16" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="34">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F17" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="4" t="s">
+    <row r="17" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F17" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="34">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:10" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F18" s="3" t="s">
+    <row r="18" spans="2:10" ht="27.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F18" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="31">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F19" s="3" t="s">
+    <row r="19" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F19" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="34">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F20" s="3" t="s">
+    <row r="20" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F20" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="34">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F21" s="3" t="s">
+    <row r="21" spans="2:10" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F21" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="29">
         <v>15</v>
       </c>
     </row>
+    <row r="22" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="25" spans="2:10" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="26" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:10" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F27" s="29" t="s">
+      <c r="F27" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G27" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H27" s="29" t="s">
+      <c r="H27" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I27" s="30" t="s">
+      <c r="I27" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J27" s="29" t="s">
+      <c r="J27" s="24" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="24"/>
-      <c r="F28" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="G28" s="20" t="s">
+      <c r="B28" s="19"/>
+      <c r="F28" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="H28" s="20" t="s">
+      <c r="H28" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="I28" s="25" t="s">
+      <c r="I28" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="J28" s="28">
+      <c r="J28" s="23">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="24"/>
-      <c r="F29" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G29" s="14" t="s">
+      <c r="B29" s="19"/>
+      <c r="F29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H29" s="20" t="s">
+      <c r="H29" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="I29" s="14" t="s">
+      <c r="I29" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="J29" s="28">
+      <c r="J29" s="23">
         <v>2</v>
       </c>
     </row>
     <row r="30" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="24"/>
-      <c r="F30" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G30" s="9" t="s">
+      <c r="B30" s="19"/>
+      <c r="F30" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I30" s="9" t="s">
+      <c r="I30" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J30" s="28">
+      <c r="J30" s="23">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="2:10" ht="31.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="24"/>
-      <c r="F31" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="G31" s="15" t="s">
+      <c r="B31" s="19"/>
+      <c r="F31" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="G31" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H31" s="20" t="s">
+      <c r="H31" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="I31" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="J31" s="28">
+      <c r="J31" s="23">
         <v>4</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="24"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="G32" s="16" t="s">
+      <c r="B32" s="19"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="G32" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="H32" s="23" t="s">
+      <c r="H32" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I32" s="16" t="s">
+      <c r="I32" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="J32" s="28">
+      <c r="J32" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="24"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="B33" s="19"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="H33" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="I33" s="32" t="s">
+      <c r="I33" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="J33" s="28">
+      <c r="J33" s="23">
         <v>6</v>
       </c>
     </row>
     <row r="34" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="24"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G34" s="14" t="s">
+      <c r="B34" s="19"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G34" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I34" s="13" t="s">
+      <c r="I34" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J34" s="28">
+      <c r="J34" s="23">
         <v>7</v>
       </c>
     </row>
     <row r="35" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="24"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G35" s="9" t="s">
+      <c r="B35" s="19"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H35" s="22" t="s">
+      <c r="H35" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="I35" s="9" t="s">
+      <c r="I35" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="J35" s="28">
+      <c r="J35" s="23">
         <v>8</v>
       </c>
     </row>
     <row r="36" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="24"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G36" s="27" t="s">
+      <c r="B36" s="19"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G36" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="H36" s="27" t="s">
+      <c r="H36" s="22" t="s">
         <v>57</v>
       </c>
       <c r="I36" t="s">
         <v>56</v>
       </c>
-      <c r="J36" s="28">
+      <c r="J36" s="23">
         <v>9</v>
       </c>
     </row>
     <row r="37" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="9"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="13" t="s">
+      <c r="B37" s="4"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="G37" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H37" s="13" t="s">
+      <c r="H37" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I37" s="14" t="s">
+      <c r="I37" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="J37" s="28">
+      <c r="J37" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="9"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G38" s="16" t="s">
+      <c r="B38" s="4"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="H38" s="23" t="s">
+      <c r="H38" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="I38" s="16" t="s">
+      <c r="I38" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="J38" s="28">
+      <c r="J38" s="23">
         <v>11</v>
       </c>
     </row>
     <row r="39" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="9"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="9"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="9"/>
-      <c r="J39" s="28">
+      <c r="B39" s="4"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="23">
         <v>12</v>
       </c>
     </row>
     <row r="40" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="9"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="28">
+      <c r="B40" s="4"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="23">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="9"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="16"/>
-      <c r="H41" s="23"/>
-      <c r="I41" s="16"/>
-      <c r="J41" s="28">
+      <c r="B41" s="4"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="23">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="9"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="16"/>
-      <c r="J42" s="28">
+      <c r="B42" s="4"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="23">
         <v>15</v>
       </c>
     </row>
     <row r="43" spans="2:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="48" spans="2:10" ht="31.5" x14ac:dyDescent="0.5">
-      <c r="I48" s="6" t="s">
+      <c r="I48" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="49" spans="6:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="50" spans="6:10" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F50" s="29" t="s">
+      <c r="F50" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="G50" s="29" t="s">
+      <c r="G50" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H50" s="29" t="s">
+      <c r="H50" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="I50" s="30" t="s">
+      <c r="I50" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="J50" s="29" t="s">
+      <c r="J50" s="24" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="51" spans="6:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F51" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G51" s="13" t="s">
+      <c r="F51" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G51" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H51" s="13" t="s">
+      <c r="H51" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I51" s="14" t="s">
+      <c r="I51" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="J51" s="28">
+      <c r="J51" s="23">
         <v>10</v>
       </c>
     </row>
     <row r="52" spans="6:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F52" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="G52" s="13" t="s">
+      <c r="F52" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G52" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="H52" s="13" t="s">
+      <c r="H52" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="I52" s="14" t="s">
+      <c r="I52" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="J52" s="13"/>
+      <c r="J52" s="8"/>
     </row>
     <row r="53" spans="6:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
     </row>
     <row r="54" spans="6:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="26"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="23"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="18"/>
     </row>
     <row r="55" spans="6:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="F55" s="9"/>
-      <c r="G55" s="17"/>
-      <c r="I55" s="9"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="12"/>
+      <c r="I55" s="4"/>
     </row>
     <row r="56" spans="6:10" x14ac:dyDescent="0.25">
-      <c r="G56" s="9"/>
+      <c r="G56" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
